--- a/tools/importer/reports/import-jsw-nev-collage.report.xlsx
+++ b/tools/importer/reports/import-jsw-nev-collage.report.xlsx
@@ -88,7 +88,7 @@
     <t>jsw-nev-collage</t>
   </si>
   <si>
-    <t>2026-10-09T07:02:25.125Z</t>
+    <t>2026-10-09T10:52:29.321Z</t>
   </si>
   <si>
     <t>https://example.com/</t>
